--- a/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
+++ b/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
@@ -736,14 +736,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45182.62504073627</v>
+        <v>45219</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="16">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -789,21 +785,6 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="16">
       <c r="A27" s="10" t="inlineStr">
         <is>
@@ -835,7 +816,7 @@
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="5" t="n">
-        <v>5443.5</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="16">
@@ -935,7 +916,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -946,18 +926,18 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A36:D36"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
+++ b/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
@@ -925,19 +925,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
+++ b/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
@@ -736,7 +736,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45219</v>
+        <v>45223</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
+++ b/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
@@ -736,7 +736,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45223</v>
+        <v>45232</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
@@ -925,19 +925,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A36:D36"/>
-    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
+++ b/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
@@ -736,7 +736,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45232</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
+++ b/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
@@ -736,7 +736,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
+++ b/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
@@ -736,7 +736,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>

--- a/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
+++ b/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
@@ -736,10 +736,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45266</v>
+        <v>45226.65156402655</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="16">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -785,6 +789,21 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="16">
       <c r="A27" s="10" t="inlineStr">
         <is>
@@ -816,7 +835,7 @@
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="5" t="n">
-        <v>6000</v>
+        <v>6423.33</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="16">
@@ -832,7 +851,7 @@
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="5" t="n">
-        <v>5742.18</v>
+        <v>6775.77</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="16">
@@ -848,7 +867,7 @@
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="5" t="n">
-        <v>6862.8</v>
+        <v>8098.1</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="16">
@@ -864,7 +883,7 @@
       </c>
       <c r="C31" s="19" t="n"/>
       <c r="D31" s="6" t="n">
-        <v>7531.98</v>
+        <v>8887.73</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="16">
@@ -880,7 +899,7 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="5" t="n">
-        <v>7831.8</v>
+        <v>9241.52</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="16">
@@ -896,7 +915,7 @@
       </c>
       <c r="C33" s="19" t="n"/>
       <c r="D33" s="6" t="n">
-        <v>8276.4</v>
+        <v>9766.15</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="16">
@@ -916,6 +935,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -926,18 +946,18 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A36:D36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
+++ b/LISTAS/ma/REGATON DE GOMA DISMAY.xlsx
@@ -736,14 +736,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45226.65156402655</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="3" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="16">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -789,21 +785,6 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="16">
       <c r="A27" s="10" t="inlineStr">
         <is>
@@ -835,7 +816,7 @@
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="5" t="n">
-        <v>6423.33</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="16">
@@ -851,7 +832,7 @@
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="5" t="n">
-        <v>6775.77</v>
+        <v>5742.18</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="16">
@@ -867,7 +848,7 @@
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="5" t="n">
-        <v>8098.1</v>
+        <v>6862.8</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="16">
@@ -883,7 +864,7 @@
       </c>
       <c r="C31" s="19" t="n"/>
       <c r="D31" s="6" t="n">
-        <v>8887.73</v>
+        <v>7531.98</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="16">
@@ -899,7 +880,7 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="5" t="n">
-        <v>9241.52</v>
+        <v>7831.8</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="16">
@@ -915,7 +896,7 @@
       </c>
       <c r="C33" s="19" t="n"/>
       <c r="D33" s="6" t="n">
-        <v>9766.15</v>
+        <v>8276.4</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="16">
@@ -935,7 +916,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -945,19 +925,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
